--- a/feedback_forms/034_employee_retirement_plan_feedback_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/034_employee_retirement_plan_feedback_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Retirement Plan Satisfaction</t>
+          <t>Retirement Plan Satisfaction 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Retirement Plan Rating</t>
+          <t>Retirement Plan Rating 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>manager_name_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manager Name</t>
+          <t>Manager Name 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Retirement Plan Rating</t>
+          <t>Retirement Plan Rating 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Retirement Plan Rating</t>
+          <t>Retirement Plan Rating 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>value_1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Value 1</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>value_2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Value 2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>value_3</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Value 3</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
